--- a/data/trans_dic/IP04F-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -513,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente</t>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 32,61</t>
+          <t>18,63; 33,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,44; 26,85</t>
+          <t>13,24; 27,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,44; 28,65</t>
+          <t>13,98; 27,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 23,25</t>
+          <t>11,02; 22,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,97; 28,83</t>
+          <t>17,99; 28,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 22,66</t>
+          <t>13,3; 22,93</t>
         </is>
       </c>
     </row>
@@ -711,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 21,48</t>
+          <t>9,65; 22,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 21,11</t>
+          <t>10,16; 21,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 26,15</t>
+          <t>12,78; 26,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 20,93</t>
+          <t>9,34; 20,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 21,78</t>
+          <t>12,74; 21,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,94; 18,61</t>
+          <t>10,86; 18,87</t>
         </is>
       </c>
     </row>
@@ -791,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 15,43</t>
+          <t>4,58; 14,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,92</t>
+          <t>5,25; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,6</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,06</t>
+          <t>2,64; 11,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 9,39</t>
+          <t>3,48; 9,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 12,29</t>
+          <t>4,67; 12,26</t>
         </is>
       </c>
     </row>
@@ -871,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 9,0</t>
+          <t>3,47; 8,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,42</t>
+          <t>2,94; 7,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,04; 7,95</t>
+          <t>2,97; 7,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,2</t>
+          <t>4,44; 10,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,45</t>
+          <t>3,96; 7,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,87</t>
+          <t>4,21; 7,67</t>
         </is>
       </c>
     </row>
@@ -951,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,35</t>
+          <t>3,08; 9,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 9,21</t>
+          <t>2,73; 9,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,09</t>
+          <t>3,14; 10,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,41</t>
+          <t>1,42; 6,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,43</t>
+          <t>3,73; 8,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,45</t>
+          <t>2,63; 6,77</t>
         </is>
       </c>
     </row>
@@ -1031,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 18,23</t>
+          <t>5,07; 18,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 15,49</t>
+          <t>3,67; 15,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,73; 15,53</t>
+          <t>4,64; 15,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,66</t>
+          <t>1,07; 8,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 14,35</t>
+          <t>5,83; 14,11</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,77</t>
+          <t>3,01; 9,94</t>
         </is>
       </c>
     </row>
@@ -1111,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,53</t>
+          <t>8,53; 12,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,17</t>
+          <t>7,56; 11,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,1</t>
+          <t>7,64; 10,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,03</t>
+          <t>6,73; 10,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,4; 10,94</t>
+          <t>8,48; 11,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,91</t>
+          <t>7,42; 9,89</t>
         </is>
       </c>
     </row>
@@ -1163,4 +1164,944 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que posee otra vivienda que se pueda utilizar como residencia aunque no la utilice habitualmente (tasa de respuesta: 99,22%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22196</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16137</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18174</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16132</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40370</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>32269</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>16411; 29215</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10938; 22418</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12348; 24600</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10998; 22568</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>31737; 49530</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24267; 41821</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>13454</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15571</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18238</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15920</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31692</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31490</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8927; 20541</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>10681; 22829</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12368; 25591</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10469; 22598</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24108; 40687</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>23592; 40981</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7715</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6213</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4509</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9803</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10722</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3947; 12490</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3220; 10714</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>626; 6098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1937; 8613</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5991; 16236</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6289; 16531</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>12117</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10899</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11472</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23589</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25118</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7099; 18391</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>6532; 16345</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6732; 17481</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>9277; 21243</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17105; 32153</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18171; 33081</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8264</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7054</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16706</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11697</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4513; 13787</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3685; 12527</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4403; 14896</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2013; 9449</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10712; 24144</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7273; 18717</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5140</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>7334</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2698; 9776</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>2240; 9586</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3434; 11782</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>718; 5751</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7421; 17953</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3863; 12751</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>69180</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>61013</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>65081</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>134261</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>118630</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>57247; 83137</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>50470; 74571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>54462; 78325</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>47291; 70423</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>117409; 153848</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>101646; 135526</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04F-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Clase-trans_dic.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 33,17</t>
+          <t>18,5; 33,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 27,13</t>
+          <t>12,9; 27,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 27,84</t>
+          <t>14,33; 28,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,02; 22,61</t>
+          <t>10,69; 23,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 28,07</t>
+          <t>17,91; 27,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 22,93</t>
+          <t>13,28; 22,91</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,65; 22,21</t>
+          <t>8,99; 21,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 21,71</t>
+          <t>10,13; 21,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 26,44</t>
+          <t>12,67; 26,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 20,16</t>
+          <t>9,38; 20,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,74; 21,5</t>
+          <t>12,69; 21,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 18,87</t>
+          <t>10,79; 18,7</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 14,5</t>
+          <t>4,86; 15,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 17,48</t>
+          <t>4,88; 17,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,72; 6,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,72</t>
+          <t>2,63; 11,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 9,42</t>
+          <t>3,15; 8,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,26</t>
+          <t>4,66; 12,61</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,99</t>
+          <t>3,73; 9,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 7,35</t>
+          <t>3,14; 8,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,7</t>
+          <t>3,16; 8,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,44; 10,17</t>
+          <t>4,29; 10,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,45</t>
+          <t>3,9; 7,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,67</t>
+          <t>4,21; 7,72</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,4</t>
+          <t>3,19; 9,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,73; 9,28</t>
+          <t>2,58; 9,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 10,62</t>
+          <t>2,8; 10,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,67</t>
+          <t>1,36; 6,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,42</t>
+          <t>3,71; 8,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,77</t>
+          <t>2,34; 6,37</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 18,37</t>
+          <t>5,03; 18,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 15,69</t>
+          <t>3,83; 15,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,64; 15,91</t>
+          <t>4,59; 14,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,56</t>
+          <t>1,07; 9,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,83; 14,11</t>
+          <t>6,1; 14,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,01; 9,94</t>
+          <t>3,03; 9,95</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,53; 12,39</t>
+          <t>8,57; 12,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,56; 11,17</t>
+          <t>7,38; 11,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,99</t>
+          <t>7,45; 10,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,02</t>
+          <t>6,54; 9,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,12</t>
+          <t>8,49; 11,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,89</t>
+          <t>7,53; 9,92</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16411; 29215</t>
+          <t>16293; 29738</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10938; 22418</t>
+          <t>10656; 22721</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12348; 24600</t>
+          <t>12660; 25184</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10998; 22568</t>
+          <t>10669; 23381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31737; 49530</t>
+          <t>31603; 49326</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24267; 41821</t>
+          <t>24217; 41783</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8927; 20541</t>
+          <t>8316; 19703</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10681; 22829</t>
+          <t>10651; 22978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12368; 25591</t>
+          <t>12259; 26087</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10469; 22598</t>
+          <t>10516; 23506</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24108; 40687</t>
+          <t>24007; 40675</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23592; 40981</t>
+          <t>23443; 40615</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3947; 12490</t>
+          <t>4186; 13212</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3220; 10714</t>
+          <t>2988; 10721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>626; 6098</t>
+          <t>621; 6015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1937; 8613</t>
+          <t>1931; 8435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5991; 16236</t>
+          <t>5428; 15124</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6289; 16531</t>
+          <t>6280; 16996</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7099; 18391</t>
+          <t>7627; 18744</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6532; 16345</t>
+          <t>6992; 17918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6732; 17481</t>
+          <t>7180; 18222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9277; 21243</t>
+          <t>8967; 21096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17105; 32153</t>
+          <t>16834; 31763</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18171; 33081</t>
+          <t>18167; 33304</t>
         </is>
       </c>
     </row>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4513; 13787</t>
+          <t>4682; 14316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3685; 12527</t>
+          <t>3487; 12359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4403; 14896</t>
+          <t>3930; 14534</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2013; 9449</t>
+          <t>1928; 8956</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10712; 24144</t>
+          <t>10650; 25015</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7273; 18717</t>
+          <t>6471; 17636</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2698; 9776</t>
+          <t>2678; 9846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2240; 9586</t>
+          <t>2338; 9361</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3434; 11782</t>
+          <t>3396; 11064</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>718; 5751</t>
+          <t>718; 6438</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7421; 17953</t>
+          <t>7766; 18330</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3863; 12751</t>
+          <t>3882; 12755</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57247; 83137</t>
+          <t>57495; 83758</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>50470; 74571</t>
+          <t>49297; 74223</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>54462; 78325</t>
+          <t>53104; 78004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47291; 70423</t>
+          <t>45961; 69967</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>117409; 153848</t>
+          <t>117500; 152171</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>101646; 135526</t>
+          <t>103183; 135976</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04F-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04F-Clase-trans_dic.xlsx
@@ -520,13 +520,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -594,22 +594,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,57%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>25,2%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>19,53%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,57%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 33,76</t>
+          <t>14,44; 28,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,9; 27,5</t>
+          <t>11,01; 23,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 28,5</t>
+          <t>18,18; 32,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,69; 23,43</t>
+          <t>13,44; 26,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,91; 27,96</t>
+          <t>17,97; 28,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 22,91</t>
+          <t>13,51; 22,66</t>
         </is>
       </c>
     </row>
@@ -674,22 +674,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>14,55%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>14,81%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,99; 21,31</t>
+          <t>12,41; 26,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 21,85</t>
+          <t>9,83; 20,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 26,96</t>
+          <t>8,61; 21,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 20,97</t>
+          <t>9,93; 21,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 21,49</t>
+          <t>12,85; 21,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,7</t>
+          <t>10,94; 18,61</t>
         </is>
       </c>
     </row>
@@ -754,22 +754,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>8,95%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,34</t>
+          <t>0,72; 6,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 17,49</t>
+          <t>2,66; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,97</t>
+          <t>4,75; 15,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,48</t>
+          <t>4,69; 17,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,77</t>
+          <t>3,26; 9,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 12,61</t>
+          <t>4,71; 12,29</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>4,9%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,16</t>
+          <t>3,04; 7,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,06</t>
+          <t>4,38; 10,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,03</t>
+          <t>3,59; 9,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,1</t>
+          <t>2,96; 7,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,36</t>
+          <t>3,95; 7,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,72</t>
+          <t>4,23; 7,87</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>5,22%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,77</t>
+          <t>2,99; 10,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,15</t>
+          <t>1,38; 6,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,36</t>
+          <t>3,03; 9,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,32</t>
+          <t>2,5; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 8,72</t>
+          <t>3,9; 8,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,37</t>
+          <t>2,6; 6,45</t>
         </is>
       </c>
     </row>
@@ -994,22 +994,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>10,21%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>8,41%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,03; 18,5</t>
+          <t>4,73; 15,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,83; 15,32</t>
+          <t>1,07; 8,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,59; 14,94</t>
+          <t>4,78; 18,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,59</t>
+          <t>3,89; 15,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,1; 14,4</t>
+          <t>5,81; 14,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,95</t>
+          <t>2,81; 9,77</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,48</t>
+          <t>7,39; 11,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,12</t>
+          <t>6,64; 10,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,94</t>
+          <t>8,53; 12,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,95</t>
+          <t>7,52; 11,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,0</t>
+          <t>8,4; 10,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,92</t>
+          <t>7,45; 9,91</t>
         </is>
       </c>
     </row>
@@ -1194,13 +1194,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -1268,22 +1268,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1306,22 +1306,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18174</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16132</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>22196</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>16137</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18174</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16132</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16293; 29738</t>
+          <t>12757; 25315</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10656; 22721</t>
+          <t>10985; 23203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12660; 25184</t>
+          <t>16018; 28722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10669; 23381</t>
+          <t>11102; 22180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31603; 49326</t>
+          <t>31715; 50870</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24217; 41783</t>
+          <t>24638; 41338</t>
         </is>
       </c>
     </row>
@@ -1386,22 +1386,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1424,22 +1424,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18238</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15920</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>13454</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>15571</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>18238</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8316; 19703</t>
+          <t>12013; 25311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10651; 22978</t>
+          <t>11022; 23456</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12259; 26087</t>
+          <t>7963; 19867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10516; 23506</t>
+          <t>10437; 22195</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24007; 40675</t>
+          <t>24322; 41216</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23443; 40615</t>
+          <t>23769; 40420</t>
         </is>
       </c>
     </row>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1542,22 +1542,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4509</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>7715</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>6213</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2088</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4509</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4186; 13212</t>
+          <t>624; 5689</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2988; 10721</t>
+          <t>1958; 8865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>621; 6015</t>
+          <t>4093; 13292</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1931; 8435</t>
+          <t>2877; 10983</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5428; 15124</t>
+          <t>5628; 16190</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6280; 16996</t>
+          <t>6349; 16568</t>
         </is>
       </c>
     </row>
@@ -1622,22 +1622,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11472</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14220</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>12117</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>10899</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11472</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14220</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7627; 18744</t>
+          <t>6907; 18045</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6992; 17918</t>
+          <t>9138; 21293</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7180; 18222</t>
+          <t>7343; 18411</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8967; 21096</t>
+          <t>6585; 16509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16834; 31763</t>
+          <t>17054; 32146</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18167; 33304</t>
+          <t>18254; 33925</t>
         </is>
       </c>
     </row>
@@ -1740,22 +1740,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1778,22 +1778,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4643</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>8264</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>7054</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8442</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4682; 14316</t>
+          <t>4197; 14151</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3487; 12359</t>
+          <t>1955; 9078</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3930; 14534</t>
+          <t>4438; 13710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1928; 8956</t>
+          <t>3375; 12433</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10650; 25015</t>
+          <t>11178; 24181</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6471; 17636</t>
+          <t>7206; 17853</t>
         </is>
       </c>
     </row>
@@ -1858,22 +1858,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1896,22 +1896,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6667</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2194</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>5435</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>5140</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6667</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2678; 9846</t>
+          <t>3499; 11498</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2338; 9361</t>
+          <t>718; 5815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3396; 11064</t>
+          <t>2544; 9700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>718; 6438</t>
+          <t>2378; 9460</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7766; 18330</t>
+          <t>7395; 18262</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3882; 12755</t>
+          <t>3605; 12526</t>
         </is>
       </c>
     </row>
@@ -1976,22 +1976,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>92</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2014,22 +2014,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>65081</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>57617</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>69180</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>61013</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>65081</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>57617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>57495; 83758</t>
+          <t>52635; 79091</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49297; 74223</t>
+          <t>46699; 70506</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53104; 78004</t>
+          <t>57267; 84105</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45961; 69967</t>
+          <t>50172; 74535</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>117500; 152171</t>
+          <t>116281; 151382</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>103183; 135976</t>
+          <t>102130; 135762</t>
         </is>
       </c>
     </row>
